--- a/2026_project/1_raw/technology_emitter.xlsx
+++ b/2026_project/1_raw/technology_emitter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutka\MT\AdOpT-NET0_dw\2026_project\1_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C83C096-E788-4889-BD2D-5A7C87E4252D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93DB6D8-6E00-48CF-978A-39FE0514C9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{B43AA277-296C-40E7-BDD7-A3E8AD46FCCB}"/>
+    <workbookView xWindow="3300" yWindow="2820" windowWidth="20100" windowHeight="13880" xr2:uid="{B43AA277-296C-40E7-BDD7-A3E8AD46FCCB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,17 +38,17 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={9ABC70C5-B8E1-4E5A-9D3F-728C92CF6A2E}</author>
+    <author>tc={517B0615-302A-42B2-9ADA-8915E9C3E2D8}</author>
     <author>tc={31FA5B2A-2065-40C9-A24C-C3B0787408B0}</author>
     <author>tc={046D910C-652B-418E-B1FB-91C9F6AD59C4}</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{9ABC70C5-B8E1-4E5A-9D3F-728C92CF6A2E}">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{517B0615-302A-42B2-9ADA-8915E9C3E2D8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    https://www.sciencedirect.com/science/article/pii/S0360544221010264</t>
+    https://pubs.acs.org/doi/10.1021/acs.iecr.8b02574</t>
       </text>
     </comment>
     <comment ref="H3" authorId="1" shapeId="0" xr:uid="{31FA5B2A-2065-40C9-A24C-C3B0787408B0}">
@@ -146,16 +146,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -210,7 +210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -237,6 +237,7 @@
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Dutkamon Wongsuvapich" id="{ADFCF73F-3C57-4941-BAAA-9DC736585725}" userId="S::DutkamonW@pttep.com::d4e1c7d0-5eb9-485b-b4a6-b9280459a798" providerId="AD"/>
+  <person displayName="Wongsuvapich, D. (Dutkamon)" id="{05C5B56A-48DF-449F-AC05-74B43AFD15F1}" userId="S::d.wongsuvapich@students.uu.nl::148e9f40-0b93-4979-85e7-cafbb3e095ad" providerId="AD"/>
 </personList>
 </file>
 
@@ -557,12 +558,12 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H2" dT="2026-03-12T20:40:57.13" personId="{ADFCF73F-3C57-4941-BAAA-9DC736585725}" id="{9ABC70C5-B8E1-4E5A-9D3F-728C92CF6A2E}">
-    <text>https://www.sciencedirect.com/science/article/pii/S0360544221010264</text>
+  <threadedComment ref="H2" dT="2026-06-20T21:37:29.32" personId="{05C5B56A-48DF-449F-AC05-74B43AFD15F1}" id="{517B0615-302A-42B2-9ADA-8915E9C3E2D8}">
+    <text>https://pubs.acs.org/doi/10.1021/acs.iecr.8b02574</text>
     <extLst>
       <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>1677990347</xltc2:checksum>
-        <xltc2:hyperlink startIndex="0" length="67" url="https://www.sciencedirect.com/science/article/pii/S0360544221010264"/>
+        <xltc2:checksum>2838639913</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="49" url="https://pubs.acs.org/doi/10.1021/acs.iecr.8b02574"/>
       </x:ext>
     </extLst>
   </threadedComment>
